--- a/RestaurantsSetup/ghazal-alreem-village/Book2.xlsx
+++ b/RestaurantsSetup/ghazal-alreem-village/Book2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohamedborsaly/restaurant-menu/RestaurantsSetup/ghazal-alreem-village/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20DEAA2-05DB-9F41-84BB-4D2FCFC075D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C25397-3199-A24B-9BD8-6BDED0D575FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1900" windowWidth="27240" windowHeight="16180" xr2:uid="{89EAB2C6-E3D1-1149-AF48-CB87DAEB172B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -124,7 +124,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -143,6 +143,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -229,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -251,6 +263,9 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,7 +710,7 @@
       <c r="C8" s="5">
         <v>48.45</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="21">
         <v>1700</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -715,7 +730,7 @@
       <c r="C9" s="5">
         <v>20.239999999999998</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="23">
         <v>700</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -732,7 +747,7 @@
       <c r="C10" s="5">
         <v>20.010000000000002</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="23">
         <v>700</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -749,7 +764,7 @@
       <c r="C11" s="5">
         <v>24.31</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="21">
         <v>825</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -764,7 +779,7 @@
       <c r="C12" s="5">
         <v>8.84</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="21">
         <v>300</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -779,7 +794,7 @@
       <c r="C13" s="12">
         <v>39.380000000000003</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="22">
         <v>1336.58</v>
       </c>
       <c r="E13" s="12" t="s">
